--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576200076</v>
+        <v>46157.93121379141</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121379141</v>
+        <v>46157.93187044818</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187044818</v>
+        <v>46157.9340768342</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9340768342</v>
+        <v>46157.93725641848</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725641848</v>
+        <v>46158.28223116368</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223116368</v>
+        <v>46158.29713025177</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713025177</v>
+        <v>46158.29823330387</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823330387</v>
+        <v>46158.33394175493</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394175493</v>
+        <v>46158.3686392458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3686392458</v>
+        <v>46158.37294921214</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
